--- a/Step7-偿付能力公司报告展示模块.xlsx
+++ b/Step7-偿付能力公司报告展示模块.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86178\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86178\Desktop\GI_Solvency_Report_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>模块ID</t>
   </si>
@@ -73,13 +73,40 @@
     <t>话术</t>
   </si>
   <si>
+    <t>行业概览</t>
+  </si>
+  <si>
+    <t>规模与发展</t>
+  </si>
+  <si>
+    <t>市场份额</t>
+  </si>
+  <si>
+    <t>underwriting_efficiency</t>
+  </si>
+  <si>
+    <t>承保效益</t>
+  </si>
+  <si>
+    <t>承保效益散点图</t>
+  </si>
+  <si>
+    <t>COMBINED_RATIO,LOSS_RATIO,EXPENSE_RATIO</t>
+  </si>
+  <si>
+    <t>{"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名"}</t>
+  </si>
+  <si>
+    <t>综合成本率、赔付率、费用率分布</t>
+  </si>
+  <si>
     <t>capability_radar</t>
   </si>
   <si>
-    <t>行业画像</t>
-  </si>
-  <si>
-    <t>能力框架</t>
+    <t>行业对标与趋势研判</t>
+  </si>
+  <si>
+    <t>能力框架-横向对标</t>
   </si>
   <si>
     <t>能力五边形</t>
@@ -94,27 +121,12 @@
     <t>{"axes":[{"code":"PREMIUM_GROWTH","label":"保费增速","period":"本季度数","lower":-10,"upper":30},{"code":"ROE","label":"ROE","period":"本年累计数","lower":0,"upper":15},{"code":"TOTAL_ASSETS","label":"总资产","period":"本季度数","lower":100000,"upper":100000000},{"code":"ACTUAL_CAPITAL","label":"实际资本","period":"本季度末数","lower":50000,"upper":30000000},{"code":"COMBINED_SOLVENCY_RATIO","label":"偿付能力","period":"本季度末数","lower":100,"upper":350}]}</t>
   </si>
   <si>
-    <t>underwriting_efficiency</t>
-  </si>
-  <si>
-    <t>承保效益</t>
-  </si>
-  <si>
-    <t>承保效益散点图</t>
-  </si>
-  <si>
-    <t>COMBINED_RATIO,LOSS_RATIO,EXPENSE_RATIO</t>
-  </si>
-  <si>
-    <t>{"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名"}</t>
-  </si>
-  <si>
-    <t>综合成本率、赔付率、费用率分布</t>
-  </si>
-  <si>
     <t>performance_pattern_grid</t>
   </si>
   <si>
+    <t>经营表现-横向对标</t>
+  </si>
+  <si>
     <t>公司业绩展示</t>
   </si>
   <si>
@@ -127,21 +139,12 @@
     <t>{"revenue_code":"SIGNED_PREMIUM","profit_code":"NET_PROFIT"}</t>
   </si>
   <si>
-    <t>solv_overview</t>
-  </si>
-  <si>
-    <t>公司规模与结构</t>
-  </si>
-  <si>
-    <t>关键偿付数据概览</t>
-  </si>
-  <si>
-    <t>关键指标表</t>
-  </si>
-  <si>
     <t>solv_ratio_combo</t>
   </si>
   <si>
+    <t>核心指标速览</t>
+  </si>
+  <si>
     <t>核心及综合充足率</t>
   </si>
   <si>
@@ -178,241 +181,40 @@
     <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]}}</t>
   </si>
   <si>
-    <t>core_capital_share</t>
-  </si>
-  <si>
-    <t>核心资本占比</t>
-  </si>
-  <si>
-    <t>资本结构组合图</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]}}</t>
-  </si>
-  <si>
-    <t>capital_efficiency_bubble</t>
-  </si>
-  <si>
-    <t>资本使用效率与核心资本占比气泡图</t>
-  </si>
-  <si>
-    <t>资本效率气泡图</t>
-  </si>
-  <si>
-    <t>ACTUAL_CAPITAL,RECOGNIZED_ASSETS,REGISTERED_CAPITAL,CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>core_capital_to_registered</t>
-  </si>
-  <si>
-    <t>核心资本/注册资本</t>
+    <t>偿付能力水平深度拆解</t>
+  </si>
+  <si>
+    <t>实际资本变动</t>
+  </si>
+  <si>
+    <t>actual_to_recognized</t>
+  </si>
+  <si>
+    <t>实际资本/认可资产率</t>
   </si>
   <si>
     <t>单指标趋势图</t>
   </si>
   <si>
-    <t>CORE_CAPITAL_TO_REGISTERED_CAPITAL</t>
-  </si>
-  <si>
-    <t>actual_to_recognized</t>
-  </si>
-  <si>
-    <t>实际资本/认可资产率</t>
-  </si>
-  <si>
     <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
   </si>
   <si>
-    <t>structure_change_1</t>
-  </si>
-  <si>
-    <t>规模与发展</t>
-  </si>
-  <si>
-    <t>承保规模</t>
-  </si>
-  <si>
-    <t>结构变化组合图</t>
-  </si>
-  <si>
-    <t>SIGNED_PREMIUM_MOTOR,SIGNED_PREMIUM</t>
-  </si>
-  <si>
-    <t>structure_change_2</t>
-  </si>
-  <si>
-    <t>经营效益</t>
-  </si>
-  <si>
-    <t>NET_PROFIT,TOTAL_ASSETS</t>
-  </si>
-  <si>
-    <t>structure_change_3</t>
-  </si>
-  <si>
-    <t>资本规模</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL,ACTUAL_CAPITAL</t>
-  </si>
-  <si>
-    <t>capital_amount_combo</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-行业资本分级</t>
-  </si>
-  <si>
-    <t>资本规模与结构</t>
-  </si>
-  <si>
-    <t>资本金额堆叠</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>core_capital_pending</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-核心资本</t>
-  </si>
-  <si>
-    <t>核心资本明细占比</t>
-  </si>
-  <si>
-    <t>构成堆叠图</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"CORE_T1_CAPITAL","label":"核心一级资本","color":"#00B8F5"},{"code":"CORE_T2_CAPITAL","label":"核心二级资本","color":"#ACEAFF"}]}</t>
-  </si>
-  <si>
-    <t>anc_capital_pending</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-附属资本</t>
-  </si>
-  <si>
-    <t>附属资本明细占比</t>
-  </si>
-  <si>
-    <t>ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"ANC_T1_CAPITAL","label":"附属一级资本","color":"#B497FF"},{"code":"ANC_T2_CAPITAL","label":"附属二级资本","color":"#7213EA"}]}</t>
-  </si>
-  <si>
-    <t>quant_risk_stack</t>
-  </si>
-  <si>
-    <t>最低资本数据对比-风险构成情况</t>
-  </si>
-  <si>
-    <t>量化风险最低资本构成</t>
-  </si>
-  <si>
-    <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"保险风险（非寿）","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"}]}</t>
-  </si>
-  <si>
-    <t>non_life_risk_liability</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-保险风险</t>
-  </si>
-  <si>
-    <t>保险风险（非寿）/认可负债率</t>
-  </si>
-  <si>
-    <t>NON_LIFE_INSURANCE_RISK_TO_LIABILITIES</t>
-  </si>
-  <si>
-    <t>market_risk_stack</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-市场风险</t>
-  </si>
-  <si>
-    <t>各类市场风险占比</t>
-  </si>
-  <si>
-    <t>INTEREST_RATE_RISK_CAPITAL,EQUITY_RISK_CAPITAL,REAL_ESTATE_RISK_CAPITAL,OVERSEAS_FIXED_INCOME_RISK_CAPITAL,OVERSEAS_EQUITY_RISK_CAPITAL,FOREIGN_EXCHANGE_RISK_CAPITAL,MARKET_RISK_DIVERSIFICATION_EFFECT,MARKET_RISK_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"MARKET_RISK_CAPITAL"}</t>
-  </si>
-  <si>
-    <t>interest_rate_to_assets</t>
-  </si>
-  <si>
-    <t>利率风险/认可资产率</t>
-  </si>
-  <si>
-    <t>INTEREST_RATE_RISK_TO_ASSETS</t>
-  </si>
-  <si>
-    <t>equity_risk_to_assets</t>
-  </si>
-  <si>
-    <t>权益价格风险/认可资产率</t>
-  </si>
-  <si>
-    <t>EQUITY_RISK_TO_ASSETS</t>
-  </si>
-  <si>
-    <t>credit_risk_stack</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-信用风险</t>
-  </si>
-  <si>
-    <t>各类信用风险占比</t>
-  </si>
-  <si>
-    <t>SPREAD_RISK_CAPITAL,COUNTERPARTY_RISK_CAPITAL,CREDIT_RISK_DIVERSIFICATION_EFFECT,CREDIT_RISK_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"CREDIT_RISK_CAPITAL"}</t>
-  </si>
-  <si>
-    <t>spread_risk_to_assets</t>
-  </si>
-  <si>
-    <t>利差风险/认可资产率</t>
-  </si>
-  <si>
-    <t>SPREAD_RISK_TO_ASSETS</t>
-  </si>
-  <si>
-    <t>counterparty_risk_to_assets</t>
-  </si>
-  <si>
-    <t>对手违约风险/认可资产率</t>
-  </si>
-  <si>
-    <t>COUNTERPARTY_RISK_TO_ASSETS</t>
-  </si>
-  <si>
-    <t>financing</t>
-  </si>
-  <si>
-    <t>附录</t>
-  </si>
-  <si>
-    <t>重大融资信息</t>
-  </si>
-  <si>
-    <t>增资发债信息统计</t>
-  </si>
-  <si>
-    <t>重大融资表</t>
+    <t>最低资本变动</t>
+  </si>
+  <si>
+    <t>经营与偿付能力联动分析</t>
+  </si>
+  <si>
+    <t>保费增速</t>
+  </si>
+  <si>
+    <t>赔付率</t>
+  </si>
+  <si>
+    <t>费用率</t>
+  </si>
+  <si>
+    <t>投资利润</t>
   </si>
 </sst>
 </file>
@@ -898,156 +700,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1361,673 +1167,372 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="15.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14.5454545454545" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.2727272727273" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:13">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2"/>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:13">
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:13">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="b">
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:13">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:13">
+      <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="b">
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:13">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:13">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="b">
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="b">
+    <row r="7" s="1" customFormat="1" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" t="b">
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" t="b">
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
+    <row r="10" s="1" customFormat="1" spans="1:13">
+      <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E9" t="s">
+      <c r="C10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:13">
+      <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G9" t="s">
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E10" t="s">
+      <c r="H11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:13">
+      <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:13">
+      <c r="B13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
+      <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:13">
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:13">
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F11" t="s">
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:13">
+      <c r="B16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" t="s">
-        <v>99</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" t="s">
-        <v>104</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" t="b">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33"/>
+      <c r="C33"/>
+      <c r="D33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
